--- a/customer_service_forms/007_retail_repair_service_referral_form--customer_service_forms.xlsx
+++ b/customer_service_forms/007_retail_repair_service_referral_form--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>american_samoa</t>
+          <t>armed_forces_-_america</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>American Samoa</t>
+          <t>Armed Forces - America</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>armed_forces_-_america</t>
+          <t>armed_forces_-_asia-pacific</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Armed Forces - America</t>
+          <t>Armed Forces - Asia-Pacific</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>armed_forces_-_asia-pacific</t>
+          <t>armed_forces_-_canada</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Armed Forces - Asia-Pacific</t>
+          <t>Armed Forces - Canada</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>armed_forces_-_canada</t>
+          <t>armed_forces_-_europe</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Armed Forces - Canada</t>
+          <t>Armed Forces - Europe</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>armed_forces_-_europe</t>
+          <t>armed_forces_-_middle_east</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Armed Forces - Europe</t>
+          <t>Armed Forces - Middle East</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>armed_forces_-_middle_east</t>
+          <t>armed_forces_-_other</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Armed Forces - Middle East</t>
+          <t>Armed Forces - Other</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>armed_forces_-_other</t>
+          <t>armed_forces_-_pacific</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Armed Forces - Other</t>
+          <t>Armed Forces - Pacific</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>armed_forces_-_pacific</t>
+          <t>armed_forces_-_united_states</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Armed Forces - Pacific</t>
+          <t>Armed Forces - United States</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>armed_forces_-_united_states</t>
+          <t>armed_forces_-_unknown</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Armed Forces - United States</t>
+          <t>Armed Forces - Unknown</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>armed_forces_-_unknown</t>
+          <t>assisted_living</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Armed Forces - Unknown</t>
+          <t>Assisted Living</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>assisted_living</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Assisted Living</t>
+          <t>Indian</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>guam</t>
+          <t>marshall_islands</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Marshall Islands</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>trust_territory_of_the_pacific_islands</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>Trust Territory of the Pacific Islands</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>marshall_islands</t>
+          <t>virgin_islands_(us)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Marshall Islands</t>
+          <t>Virgin Islands (US)</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>northern_mariana_islands</t>
+          <t>armed_forces_-_africa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Northern Mariana Islands</t>
+          <t>Armed Forces - Africa</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>puerto_rico</t>
+          <t>armed_forces_-_americas</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Armed Forces - Americas</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>trust_territory_of_the_pacific_islands</t>
+          <t>armed_forces_-_asia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Trust Territory of the Pacific Islands</t>
+          <t>Armed Forces - Asia</t>
         </is>
       </c>
     </row>
@@ -2423,316 +2423,163 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>virgin_islands</t>
+          <t>armed_forces_-_caribbean</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Virgin Islands</t>
+          <t>Armed Forces - Caribbean</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>customer_state_choices</t>
+          <t>repair_status_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>virgin_islands_(us)</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Virgin Islands (US)</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>customer_state_choices</t>
+          <t>repair_status_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>armed_forces_-_africa</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Armed Forces - Africa</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>customer_state_choices</t>
+          <t>repair_status_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>armed_forces_-_americas</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Armed Forces - Americas</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>customer_state_choices</t>
+          <t>repair_status_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>armed_forces_-_asia</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Armed Forces - Asia</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>customer_state_choices</t>
+          <t>repair_status_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>armed_forces_-_caribbean</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Armed Forces - Caribbean</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>customer_state_choices</t>
+          <t>customer_service_rep_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>armed_forces_-_europe</t>
+          <t>rep_a</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Armed Forces - Europe</t>
+          <t>Rep A</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>customer_state_choices</t>
+          <t>customer_service_rep_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>armed_forces_-_middle_east</t>
+          <t>rep_b</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Armed Forces - Middle East</t>
+          <t>Rep B</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>customer_state_choices</t>
+          <t>customer_service_rep_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>armed_forces_-_pacific</t>
+          <t>rep_c</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Armed Forces - Pacific</t>
+          <t>Rep C</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>customer_state_choices</t>
+          <t>customer_service_rep_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>armed_forces_-_unknown</t>
+          <t>rep_d</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
-        <is>
-          <t>Armed Forces - Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>repair_status_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>repair_status_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>repair_status_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>repair_status_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>repair_status_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>customer_service_rep_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>rep_a</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Rep A</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>customer_service_rep_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>rep_b</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Rep B</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>customer_service_rep_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>rep_c</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Rep C</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>customer_service_rep_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>rep_d</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
         <is>
           <t>Rep D</t>
         </is>
